--- a/SRPT.xlsx
+++ b/SRPT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A88648B-57AD-417C-98E6-BE8BB7213BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804A093F-01AE-4769-A2FF-BDC3218E2410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6490" yWindow="8380" windowWidth="27450" windowHeight="11540" activeTab="1" xr2:uid="{79CAE26F-8736-4C5E-9FC6-A2D7A01B0567}"/>
+    <workbookView xWindow="17460" yWindow="6790" windowWidth="19170" windowHeight="13220" activeTab="1" xr2:uid="{79CAE26F-8736-4C5E-9FC6-A2D7A01B0567}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -44,12 +44,16 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={E6AB6E99-1C3B-4950-9986-65466B8F87A6}</author>
+    <author>tc={04498D6E-3C18-4A5B-A908-2E60D972CB97}</author>
+    <author>tc={24D42E51-CC70-433B-B635-28ADB495B3B2}</author>
     <author>tc={6230A4A9-C9AF-4BE7-99BF-B573BD017A22}</author>
     <author>tc={CBA3C9AE-8CDE-4C14-99CA-A98DB0CE1BE6}</author>
     <author>tc={5AFD68C2-EA74-46FE-BF40-AB537FB76AE8}</author>
     <author>tc={7C3EC1BA-FB3C-4FE0-8E5F-1192557AF098}</author>
+    <author>tc={4F81179F-16E6-41BC-B914-AFAB95CADEE2}</author>
     <author>tc={79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}</author>
     <author>tc={4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}</author>
+    <author>tc={9D7C51D0-BE73-45DC-971C-65116E6017D9}</author>
   </authors>
   <commentList>
     <comment ref="V6" authorId="0" shapeId="0" xr:uid="{E6AB6E99-1C3B-4950-9986-65466B8F87A6}">
@@ -60,7 +64,23 @@
     600 patients on therapy</t>
       </text>
     </comment>
-    <comment ref="W13" authorId="1" shapeId="0" xr:uid="{6230A4A9-C9AF-4BE7-99BF-B573BD017A22}">
+    <comment ref="AA6" authorId="1" shapeId="0" xr:uid="{04498D6E-3C18-4A5B-A908-2E60D972CB97}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Consensus $95m</t>
+      </text>
+    </comment>
+    <comment ref="AA7" authorId="2" shapeId="0" xr:uid="{24D42E51-CC70-433B-B635-28ADB495B3B2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    $226m consensus</t>
+      </text>
+    </comment>
+    <comment ref="W13" authorId="3" shapeId="0" xr:uid="{6230A4A9-C9AF-4BE7-99BF-B573BD017A22}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -68,7 +88,7 @@
     5/6/25 consensus 687m </t>
       </text>
     </comment>
-    <comment ref="X13" authorId="2" shapeId="0" xr:uid="{CBA3C9AE-8CDE-4C14-99CA-A98DB0CE1BE6}">
+    <comment ref="X13" authorId="4" shapeId="0" xr:uid="{CBA3C9AE-8CDE-4C14-99CA-A98DB0CE1BE6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -76,7 +96,7 @@
     5/6/25 consensus 741m</t>
       </text>
     </comment>
-    <comment ref="Y13" authorId="3" shapeId="0" xr:uid="{5AFD68C2-EA74-46FE-BF40-AB537FB76AE8}">
+    <comment ref="Y13" authorId="5" shapeId="0" xr:uid="{5AFD68C2-EA74-46FE-BF40-AB537FB76AE8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +105,7 @@
 11/3/25 consensus: 336m</t>
       </text>
     </comment>
-    <comment ref="Z13" authorId="4" shapeId="0" xr:uid="{7C3EC1BA-FB3C-4FE0-8E5F-1192557AF098}">
+    <comment ref="Z13" authorId="6" shapeId="0" xr:uid="{7C3EC1BA-FB3C-4FE0-8E5F-1192557AF098}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -94,7 +114,15 @@
 11/3/25 consensus: 351m</t>
       </text>
     </comment>
-    <comment ref="AU13" authorId="5" shapeId="0" xr:uid="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
+    <comment ref="AA13" authorId="7" shapeId="0" xr:uid="{4F81179F-16E6-41BC-B914-AFAB95CADEE2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    474m consensus 5/4/26</t>
+      </text>
+    </comment>
+    <comment ref="AU13" authorId="8" shapeId="0" xr:uid="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -103,12 +131,21 @@
 Consensus 3.0B</t>
       </text>
     </comment>
-    <comment ref="AV13" authorId="6" shapeId="0" xr:uid="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
+    <comment ref="AV13" authorId="9" shapeId="0" xr:uid="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    5/6/25 consensus 3.76B</t>
+    5/6/25 consensus 3.76B
+3/20/26 consensus 1.71B</t>
+      </text>
+    </comment>
+    <comment ref="AW13" authorId="10" shapeId="0" xr:uid="{9D7C51D0-BE73-45DC-971C-65116E6017D9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    3/20/26 consensus 1.44B</t>
       </text>
     </comment>
   </commentList>
@@ -116,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="259">
   <si>
     <t>Price</t>
   </si>
@@ -787,9 +824,6 @@
     <t>IND 2H25</t>
   </si>
   <si>
-    <t>ARO-HTT</t>
-  </si>
-  <si>
     <t>Huntington's</t>
   </si>
   <si>
@@ -890,13 +924,19 @@
   </si>
   <si>
     <t>Q426</t>
+  </si>
+  <si>
+    <t>PPE</t>
+  </si>
+  <si>
+    <t>SRP-1005 (ARO-HTT)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -923,6 +963,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1773,6 +1819,12 @@
   <threadedComment ref="V6" dT="2025-03-21T16:35:25.37" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{E6AB6E99-1C3B-4950-9986-65466B8F87A6}">
     <text>600 patients on therapy</text>
   </threadedComment>
+  <threadedComment ref="AA6" dT="2026-05-04T14:36:08.27" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{04498D6E-3C18-4A5B-A908-2E60D972CB97}">
+    <text>Consensus $95m</text>
+  </threadedComment>
+  <threadedComment ref="AA7" dT="2026-05-04T14:36:22.45" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{24D42E51-CC70-433B-B635-28ADB495B3B2}">
+    <text>$226m consensus</text>
+  </threadedComment>
   <threadedComment ref="W13" dT="2025-05-06T15:45:31.88" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{6230A4A9-C9AF-4BE7-99BF-B573BD017A22}">
     <text xml:space="preserve">5/6/25 consensus 687m </text>
   </threadedComment>
@@ -1787,12 +1839,19 @@
     <text>5/6/25 consensus 828m
 11/3/25 consensus: 351m</text>
   </threadedComment>
+  <threadedComment ref="AA13" dT="2026-05-04T14:14:19.13" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{4F81179F-16E6-41BC-B914-AFAB95CADEE2}">
+    <text>474m consensus 5/4/26</text>
+  </threadedComment>
   <threadedComment ref="AU13" dT="2025-05-06T15:53:17.18" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
     <text>Q424 product guidance: 2.9-3.1B
 Consensus 3.0B</text>
   </threadedComment>
   <threadedComment ref="AV13" dT="2025-05-06T15:46:11.33" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
-    <text>5/6/25 consensus 3.76B</text>
+    <text>5/6/25 consensus 3.76B
+3/20/26 consensus 1.71B</text>
+  </threadedComment>
+  <threadedComment ref="AW13" dT="2026-03-20T13:47:21.26" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{9D7C51D0-BE73-45DC-971C-65116E6017D9}">
+    <text>3/20/26 consensus 1.44B</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1830,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -1845,10 +1904,11 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>97</v>
+        <f>105.615096-0.650876</f>
+        <v>104.96422</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
@@ -1873,7 +1933,7 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>1261</v>
+        <v>2204.2486199999998</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
@@ -1888,10 +1948,11 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>786</v>
+        <f>801.282+138.368</f>
+        <v>939.65000000000009</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
@@ -1906,10 +1967,10 @@
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>1138</v>
+        <v>828.97400000000005</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -1928,7 +1989,7 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>1613</v>
+        <v>2093.5726199999999</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -1963,10 +2024,10 @@
         <v>45</v>
       </c>
       <c r="L9" s="2">
-        <v>5801.1610000000001</v>
+        <v>6042.5860000000002</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
@@ -1987,10 +2048,10 @@
         <v>46</v>
       </c>
       <c r="L10" s="2">
-        <v>4658.482</v>
+        <v>4876.9840000000004</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
@@ -2028,6 +2089,15 @@
         <v>111</v>
       </c>
       <c r="I12" s="10"/>
+      <c r="K12" t="s">
+        <v>257</v>
+      </c>
+      <c r="L12" s="2">
+        <v>345.125</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
@@ -2130,13 +2200,13 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="C19" t="s">
         <v>223</v>
       </c>
-      <c r="C19" t="s">
-        <v>224</v>
-      </c>
       <c r="D19" s="29" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
         <v>221</v>
@@ -2148,16 +2218,16 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D20" s="29" t="s">
         <v>169</v>
       </c>
       <c r="E20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F20" t="s">
         <v>111</v>
@@ -2166,16 +2236,16 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D21" s="29" t="s">
         <v>169</v>
       </c>
       <c r="E21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F21" t="s">
         <v>111</v>
@@ -2311,16 +2381,16 @@
         <v>63</v>
       </c>
       <c r="AA2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB2" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AD2" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="AF2">
         <v>2010</v>
@@ -2640,6 +2710,9 @@
       <c r="Z6" s="2">
         <v>110.4</v>
       </c>
+      <c r="AA6" s="2">
+        <v>95</v>
+      </c>
       <c r="AS6" s="2">
         <f>SUM(O6:R6)</f>
         <v>200.29999999999998</v>
@@ -2738,6 +2811,9 @@
       <c r="Z7" s="2">
         <v>259.2</v>
       </c>
+      <c r="AA7" s="2">
+        <v>226</v>
+      </c>
       <c r="AL7" s="2">
         <f t="shared" ref="AL7:AR7" si="15">+AL13</f>
         <v>5.4</v>
@@ -2960,6 +3036,10 @@
         <f>+Z7+Z6</f>
         <v>369.6</v>
       </c>
+      <c r="AA11" s="2">
+        <f>+AA7+AA6</f>
+        <v>321</v>
+      </c>
       <c r="AS11" s="2">
         <f t="shared" ref="AS11:AT11" si="20">+AS7+AS6</f>
         <v>1144.876</v>
@@ -3069,8 +3149,10 @@
         <v>29.312999999999999</v>
       </c>
       <c r="Z12" s="2">
-        <f>+Y12</f>
-        <v>29.312999999999999</v>
+        <v>73.326999999999998</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:57" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -3144,7 +3226,23 @@
       </c>
       <c r="Z13" s="6">
         <f t="shared" si="22"/>
-        <v>398.91300000000001</v>
+        <v>442.92700000000002</v>
+      </c>
+      <c r="AA13" s="6">
+        <f>+AA11+AA12</f>
+        <v>371</v>
+      </c>
+      <c r="AB13" s="6">
+        <f>+AB11+AB12</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="6">
+        <f>+AC11+AC12</f>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6">
+        <f>+AD11+AD12</f>
+        <v>0</v>
       </c>
       <c r="AL13" s="6">
         <v>5.4</v>
@@ -3277,7 +3375,7 @@
       </c>
       <c r="Z14" s="2">
         <f>+Z13*0.18</f>
-        <v>71.804339999999996</v>
+        <v>79.726860000000002</v>
       </c>
       <c r="AS14" s="2">
         <f t="shared" ref="AS14:AS17" si="25">SUM(O14:R14)</f>
@@ -3289,7 +3387,7 @@
       </c>
       <c r="AU14" s="2">
         <f t="shared" ref="AU14" si="27">SUM(W14:Z14)</f>
-        <v>512.70133999999996</v>
+        <v>520.62385999999992</v>
       </c>
       <c r="AV14" s="2">
         <f>+AV13-AV15</f>
@@ -3403,7 +3501,7 @@
       </c>
       <c r="Z15" s="2">
         <f t="shared" si="30"/>
-        <v>327.10865999999999</v>
+        <v>363.20014000000003</v>
       </c>
       <c r="AS15" s="2">
         <f>+AS13-AS14</f>
@@ -3415,7 +3513,7 @@
       </c>
       <c r="AU15" s="2">
         <f>+AU13-AU14</f>
-        <v>1352.0216599999999</v>
+        <v>1344.09914</v>
       </c>
       <c r="AV15" s="2">
         <f>+AV13*0.85</f>
@@ -3514,6 +3612,9 @@
       <c r="Y16" s="2">
         <v>218.89</v>
       </c>
+      <c r="Z16" s="2">
+        <v>325.33600000000001</v>
+      </c>
       <c r="AS16" s="2">
         <f t="shared" si="25"/>
         <v>877.38699999999994</v>
@@ -3577,6 +3678,9 @@
       </c>
       <c r="Y17" s="2">
         <v>91.893000000000001</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>128.297</v>
       </c>
       <c r="AS17" s="2">
         <f t="shared" si="25"/>
@@ -3702,7 +3806,7 @@
       </c>
       <c r="Z18" s="2">
         <f>+Z17+Z16</f>
-        <v>0</v>
+        <v>453.63300000000004</v>
       </c>
       <c r="AS18" s="2">
         <f>+AS16+AS17</f>
@@ -3828,7 +3932,7 @@
       </c>
       <c r="Z19" s="2">
         <f>+Z15-Z18</f>
-        <v>327.10865999999999</v>
+        <v>-90.432860000000005</v>
       </c>
       <c r="AS19" s="2">
         <f>+AS15-AS18</f>
@@ -3840,7 +3944,7 @@
       </c>
       <c r="AU19" s="2">
         <f>+AU15-AU18</f>
-        <v>793.5496599999999</v>
+        <v>785.62714000000005</v>
       </c>
       <c r="AV19" s="2">
         <f t="shared" ref="AV19" si="47">+AV15-AV18</f>
@@ -3936,6 +4040,9 @@
         <v>38.061</v>
       </c>
       <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2">
         <v>0</v>
       </c>
       <c r="AS20" s="2">
@@ -4018,7 +4125,7 @@
       </c>
       <c r="Z21" s="2">
         <f>+Z19+Z20</f>
-        <v>327.10865999999999</v>
+        <v>-90.432860000000005</v>
       </c>
       <c r="AS21" s="2">
         <f>+AS19+AS20</f>
@@ -4030,7 +4137,7 @@
       </c>
       <c r="AU21" s="2">
         <f>+AU19+AU20</f>
-        <v>793.5496599999999</v>
+        <v>785.62714000000005</v>
       </c>
       <c r="AV21" s="2">
         <f t="shared" ref="AV21:BE21" si="60">+AV19+AV20</f>
@@ -4129,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS22" s="2">
         <f t="shared" ref="AS22" si="61">SUM(O22:R22)</f>
@@ -4141,7 +4248,7 @@
       </c>
       <c r="AU22" s="2">
         <f>+AU21*0.2</f>
-        <v>158.70993199999998</v>
+        <v>157.12542800000003</v>
       </c>
       <c r="AV22" s="2">
         <f t="shared" ref="AV22:BE22" si="63">+AV21*0.2</f>
@@ -4255,7 +4362,7 @@
       </c>
       <c r="Z23" s="2">
         <f>+Z21-Z22</f>
-        <v>327.10865999999999</v>
+        <v>-94.432860000000005</v>
       </c>
       <c r="AS23" s="2">
         <f>+AS21-AS22</f>
@@ -4267,7 +4374,7 @@
       </c>
       <c r="AU23" s="2">
         <f>+AU21-AU22</f>
-        <v>634.83972799999992</v>
+        <v>628.501712</v>
       </c>
       <c r="AV23" s="2">
         <f t="shared" ref="AV23:BE23" si="65">+AV21-AV22</f>
@@ -4372,7 +4479,7 @@
       </c>
       <c r="Z24" s="1">
         <f t="shared" si="66"/>
-        <v>3.2633524546824026</v>
+        <v>-0.90113709885202253</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
@@ -4380,7 +4487,7 @@
       <c r="AD24" s="1"/>
       <c r="AU24" s="1">
         <f>+AU23/AU25</f>
-        <v>5.8524598336928655</v>
+        <v>5.7940309382893593</v>
       </c>
       <c r="AV24" s="1">
         <f t="shared" ref="AV24:BE24" si="67">+AV23/AV25</f>
@@ -4479,8 +4586,7 @@
         <v>100.23699999999999</v>
       </c>
       <c r="Z25" s="2">
-        <f>+Y25</f>
-        <v>100.23699999999999</v>
+        <v>104.79300000000001</v>
       </c>
       <c r="AS25" s="2">
         <f>R25</f>
@@ -4537,7 +4643,7 @@
     </row>
     <row r="26" spans="2:60" x14ac:dyDescent="0.25">
       <c r="BG26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BH26" s="22">
         <v>0.09</v>
@@ -4545,7 +4651,7 @@
     </row>
     <row r="27" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V27" s="22">
         <f t="shared" ref="V27:W27" si="69">+V13/R13-1</f>
@@ -4565,9 +4671,12 @@
       </c>
       <c r="Z27" s="22">
         <f>+Z13/V13-1</f>
-        <v>-0.39416816638950269</v>
-      </c>
-      <c r="AA27" s="22"/>
+        <v>-0.32732381104251618</v>
+      </c>
+      <c r="AA27" s="22">
+        <f>+AA13/W13-1</f>
+        <v>-0.50223591334343176</v>
+      </c>
       <c r="AB27" s="22"/>
       <c r="AC27" s="22"/>
       <c r="AD27" s="22"/>
@@ -4611,9 +4720,12 @@
       </c>
       <c r="Z28" s="22">
         <f>+Z15/Z13</f>
-        <v>0.82</v>
-      </c>
-      <c r="AA28" s="22"/>
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="AA28" s="22">
+        <f>+AA15/AA13</f>
+        <v>0</v>
+      </c>
       <c r="AB28" s="22"/>
       <c r="AC28" s="22"/>
       <c r="AD28" s="22"/>
@@ -4626,11 +4738,11 @@
         <v>0.821536191746009</v>
       </c>
       <c r="BG28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="BH28" s="2">
         <f>NPV(BH26,AV23:BE23)+Main!L5-Main!L6</f>
-        <v>3321.8851295339864</v>
+        <v>3784.5611295339868</v>
       </c>
     </row>
     <row r="29" spans="2:60" x14ac:dyDescent="0.25">
@@ -4644,7 +4756,7 @@
       </c>
       <c r="BH29" s="1">
         <f>+BH28/Main!L3</f>
-        <v>34.246238448803986</v>
+        <v>36.055725746678121</v>
       </c>
     </row>
     <row r="31" spans="2:60" x14ac:dyDescent="0.25">
@@ -4663,6 +4775,10 @@
         <f>+Y32-Y50</f>
         <v>-183.15300000000002</v>
       </c>
+      <c r="Z31" s="2">
+        <f>+Z32-Z50</f>
+        <v>111.72400000000005</v>
+      </c>
     </row>
     <row r="32" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
@@ -4676,8 +4792,12 @@
         <f>613.077+237.916+1</f>
         <v>851.99299999999994</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z32" s="2">
+        <f>801.282+138.368+1.048</f>
+        <v>940.69800000000009</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
         <v>139</v>
       </c>
@@ -4687,8 +4807,11 @@
       <c r="Y33" s="2">
         <v>395.73899999999998</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z33" s="2">
+        <v>398.233</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>140</v>
       </c>
@@ -4699,8 +4822,11 @@
         <f>1077.166</f>
         <v>1077.1659999999999</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z34" s="2">
+        <v>914.74400000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>141</v>
       </c>
@@ -4710,8 +4836,11 @@
       <c r="Y35" s="2">
         <v>206.06200000000001</v>
       </c>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z35" s="2">
+        <v>113.455</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>142</v>
       </c>
@@ -4721,8 +4850,11 @@
       <c r="Y36" s="2">
         <v>192.34899999999999</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z36" s="2">
+        <v>171.85599999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>143</v>
       </c>
@@ -4732,8 +4864,11 @@
       <c r="Y37" s="2">
         <v>358.93599999999998</v>
       </c>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z37" s="2">
+        <v>345.125</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>144</v>
       </c>
@@ -4743,8 +4878,11 @@
       <c r="Y38" s="2">
         <v>139.167</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z38" s="2">
+        <v>125.495</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>145</v>
       </c>
@@ -4754,8 +4892,11 @@
       <c r="Y39" s="2">
         <v>198.601</v>
       </c>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z39" s="2">
+        <v>184.54300000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>146</v>
       </c>
@@ -4765,8 +4906,11 @@
       <c r="Y40" s="2">
         <v>73.384</v>
       </c>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z40" s="2">
+        <v>155.554</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>147</v>
       </c>
@@ -4782,8 +4926,12 @@
         <f>SUM(Y32:Y40)</f>
         <v>3493.3970000000004</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z41" s="2">
+        <f>SUM(Z32:Z40)</f>
+        <v>3349.703</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>150</v>
       </c>
@@ -4793,8 +4941,11 @@
       <c r="Y43" s="2">
         <v>94.015000000000001</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z43" s="2">
+        <v>280.84100000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>151</v>
       </c>
@@ -4804,8 +4955,11 @@
       <c r="Y44" s="2">
         <v>295.79300000000001</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z44" s="2">
+        <v>359.65899999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>152</v>
       </c>
@@ -4816,8 +4970,12 @@
       <c r="Y45" s="2">
         <v>485.44900000000001</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z45" s="2">
+        <f>443.397+83.91</f>
+        <v>527.30700000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>153</v>
       </c>
@@ -4827,8 +4985,11 @@
       <c r="Y46" s="2">
         <v>10.167999999999999</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z46" s="2">
+        <v>11.393000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>154</v>
       </c>
@@ -4838,8 +4999,11 @@
       <c r="Y47" s="2">
         <v>215.042</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z47" s="2">
+        <v>199.37799999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>155</v>
       </c>
@@ -4850,8 +5014,11 @@
         <f>36+0.3</f>
         <v>36.299999999999997</v>
       </c>
-    </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>156</v>
       </c>
@@ -4861,8 +5028,11 @@
       <c r="Y49" s="2">
         <v>1.4039999999999999</v>
       </c>
-    </row>
-    <row r="50" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z49" s="2">
+        <v>1.5289999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>4</v>
       </c>
@@ -4872,19 +5042,25 @@
       <c r="Y50" s="2">
         <v>1035.146</v>
       </c>
-    </row>
-    <row r="51" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z50" s="2">
+        <v>828.97400000000005</v>
+      </c>
+    </row>
+    <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>149</v>
       </c>
       <c r="W51" s="2">
         <v>1142.723</v>
       </c>
-      <c r="Y51">
+      <c r="Y51" s="2">
         <v>1320.12</v>
       </c>
-    </row>
-    <row r="52" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z51" s="2">
+        <v>1140.6220000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>148</v>
       </c>
@@ -4900,10 +5076,14 @@
         <f>SUM(Y43:Y51)</f>
         <v>3493.4369999999999</v>
       </c>
-    </row>
-    <row r="54" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z52" s="2">
+        <f>SUM(Z43:Z51)</f>
+        <v>3349.7030000000004</v>
+      </c>
+    </row>
+    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="W54" s="2">
         <f>+W23</f>
@@ -4917,10 +5097,14 @@
         <f>+Y23</f>
         <v>-62.245000000000033</v>
       </c>
-    </row>
-    <row r="55" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z54" s="2">
+        <f>+Z23</f>
+        <v>-94.432860000000005</v>
+      </c>
+    </row>
+    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="W55" s="2">
         <v>-447.50799999999998</v>
@@ -4930,9 +5114,9 @@
         <v>196.89199999999997</v>
       </c>
     </row>
-    <row r="56" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W56" s="2">
         <v>90.727999999999994</v>
@@ -4942,9 +5126,9 @@
         <v>-36.720999999999997</v>
       </c>
     </row>
-    <row r="57" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W57" s="2">
         <v>41.427999999999997</v>
@@ -4954,9 +5138,9 @@
         <v>37.025000000000006</v>
       </c>
     </row>
-    <row r="58" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W58" s="2">
         <v>9.9779999999999998</v>
@@ -4966,7 +5150,7 @@
         <v>10.840000000000002</v>
       </c>
     </row>
-    <row r="59" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>144</v>
       </c>
@@ -4978,9 +5162,9 @@
         <v>4.0220000000000002</v>
       </c>
     </row>
-    <row r="60" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W60" s="2">
         <v>-1.9119999999999999</v>
@@ -4990,9 +5174,9 @@
         <v>-1.8660000000000001</v>
       </c>
     </row>
-    <row r="61" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W61" s="2">
         <v>1.6919999999999999</v>
@@ -5002,9 +5186,9 @@
         <v>1.611</v>
       </c>
     </row>
-    <row r="62" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W62" s="2">
         <f>-57.383+71.136-177.359-15.067-85.397-17.707</f>
@@ -5015,9 +5199,9 @@
         <v>49.53400000000002</v>
       </c>
     </row>
-    <row r="63" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W63" s="2">
         <f>SUM(W55:W62)</f>
@@ -5027,10 +5211,18 @@
         <f>SUM(X55:X62)</f>
         <v>261.33699999999999</v>
       </c>
+      <c r="Y63" s="2">
+        <f>SUM(Y55:Y62)</f>
+        <v>0</v>
+      </c>
+      <c r="Z63" s="2">
+        <f>SUM(Z55:Z62)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -5057,7 +5249,7 @@
     </row>
     <row r="66" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -5085,7 +5277,7 @@
     </row>
     <row r="67" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -5112,7 +5304,7 @@
     </row>
     <row r="68" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -5139,7 +5331,7 @@
     </row>
     <row r="69" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -5167,7 +5359,7 @@
     </row>
     <row r="71" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -5194,7 +5386,7 @@
     </row>
     <row r="72" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -5221,7 +5413,7 @@
     </row>
     <row r="73" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -5248,7 +5440,7 @@
     </row>
     <row r="74" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
@@ -5276,7 +5468,7 @@
     </row>
     <row r="75" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -5839,7 +6031,7 @@
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6098,7 +6290,7 @@
     </row>
     <row r="29" spans="3:7" ht="13" x14ac:dyDescent="0.3">
       <c r="C29" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
